--- a/Assets/Resource/Summon/PicList.xlsx
+++ b/Assets/Resource/Summon/PicList.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EA431A-02F6-46F0-9463-97F95FEDF721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD45DEDD-ACC2-4DE8-AF3E-980B452E6421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
   <si>
     <t>01</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,10 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对方攻击力最高的单位的攻击无法击败你（但不免疫附加效果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>两侧动物的防御力加1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -413,10 +409,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>若击败了敌方动物，则继续攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -433,22 +425,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>‌打出时，所有防御力为一的敌人立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，己方法师立即恢复一点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>‌打出时，己方法师的生命值可以变为 对方法师的生命值减一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的防御力锁定为零，但是拥有三点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>打出时，你的场上的剩余空位都替换为幽灵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -488,15 +464,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>打出时，己方法师立即恢复一点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>打出时，若面前的敌人的攻击力小于你，则其立即死亡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>打出时，所有防御力为一的敌人立即死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时，己方法师立即恢复2点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打出时，己方法师的生命值可以变为与 对方法师的生命值相等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使你左边和右边的敌人的防御力均不会超过二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‌对方攻击力最高的单位的攻击无法击败你（但不免疫附加效果）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使面前的动物防御力减2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +496,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,6 +518,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -551,7 +550,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -562,6 +561,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1736,13 +1738,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>158808</xdr:colOff>
+      <xdr:colOff>49950</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>57233</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9044</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>506676</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>481834</xdr:rowOff>
     </xdr:to>
@@ -1773,8 +1775,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="158808" y="10534733"/>
-          <a:ext cx="459836" cy="423287"/>
+          <a:off x="49950" y="12498049"/>
+          <a:ext cx="456726" cy="424601"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2989,7 +2991,7 @@
         <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1">
         <v>4</v>
@@ -2998,7 +3000,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3009,7 +3011,7 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1">
         <v>3</v>
@@ -3018,7 +3020,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3029,7 +3031,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -3038,7 +3040,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3049,7 +3051,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -3058,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3069,7 +3071,7 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
@@ -3078,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3098,7 +3100,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3109,7 +3111,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3118,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3129,7 +3131,7 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -3138,7 +3140,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3149,7 +3151,7 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
@@ -3158,7 +3160,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3168,8 +3170,8 @@
       <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
-        <v>115</v>
+      <c r="D10" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3178,7 +3180,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3189,7 +3191,7 @@
         <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3198,7 +3200,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3206,10 +3208,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -3218,7 +3220,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3229,7 +3231,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
@@ -3238,7 +3240,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,7 +3251,7 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -3258,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3269,7 +3271,7 @@
         <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -3278,7 +3280,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3298,7 +3300,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3309,7 +3311,7 @@
         <v>54</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -3318,7 +3320,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3329,7 +3331,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -3338,7 +3340,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3349,7 +3351,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -3358,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3369,7 +3371,7 @@
         <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
@@ -3378,7 +3380,7 @@
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3389,7 +3391,7 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -3398,7 +3400,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3409,7 +3411,7 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3418,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3429,7 +3431,7 @@
         <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3438,7 +3440,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,10 +3448,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="1">
         <v>5</v>
@@ -3458,7 +3460,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3469,7 +3471,7 @@
         <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="1">
         <v>5</v>
@@ -3478,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3489,7 +3491,7 @@
         <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3498,7 +3500,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3509,7 +3511,7 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -3518,7 +3520,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3529,7 +3531,7 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -3538,7 +3540,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3549,7 +3551,7 @@
         <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -3558,7 +3560,7 @@
         <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,7 +3580,7 @@
         <v>3</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3589,7 +3591,7 @@
         <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
@@ -3598,7 +3600,7 @@
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3609,7 +3611,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -3618,7 +3620,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3629,7 +3631,7 @@
         <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -3638,7 +3640,7 @@
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3649,7 +3651,7 @@
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -3658,7 +3660,7 @@
         <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3669,7 +3671,7 @@
         <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35" s="1">
         <v>4</v>
@@ -3678,7 +3680,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3689,7 +3691,7 @@
         <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E36" s="1">
         <v>4</v>
@@ -3698,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3706,10 +3708,10 @@
         <v>73</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -3718,7 +3720,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3729,7 +3731,7 @@
         <v>74</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -3738,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3749,7 +3751,7 @@
         <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3758,7 +3760,7 @@
         <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3769,7 +3771,7 @@
         <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3778,47 +3780,47 @@
         <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Summon/PicList.xlsx
+++ b/Assets/Resource/Summon/PicList.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD45DEDD-ACC2-4DE8-AF3E-980B452E6421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551040B9-F05E-4D72-A063-061FD33C52EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="139">
   <si>
     <t>01</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -289,206 +289,202 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝎子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你场上的动物死亡时，你可以立即将幽灵打出（此效果不可继承）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽灵</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>海胆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变色龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>袋鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时，对方的实际防御力等于其攻击力或防御力中的较小值</t>
+  </si>
+  <si>
+    <t>死亡时，你场上的空位都替换为幽灵</t>
+  </si>
+  <si>
+    <t>死亡时，会使面前的敌人立即死亡</t>
+  </si>
+  <si>
+    <t>打出时，若面前的敌人的防御力大于你，则其立即死亡</t>
+  </si>
+  <si>
+    <t>受到攻击后，会立即进行一次攻击（即使已经死亡）</t>
+  </si>
+  <si>
+    <t>打出时，若面前存在敌人，会立即进行一次攻击</t>
+  </si>
+  <si>
+    <t>攻击时，你会同时攻击左侧和右侧（侧面如果是墙壁则不产生效果）</t>
+  </si>
+  <si>
+    <t>攻击时，你会同时攻击左侧和面前（侧面如果是墙壁则不产生效果）</t>
+  </si>
+  <si>
+    <t>攻击时，你会同时攻击面前和右侧（侧面如果是墙壁则不产生效果）</t>
+  </si>
+  <si>
+    <t>打出时和死亡时，使一个 防御力为一的敌人 立即死亡</t>
+  </si>
+  <si>
+    <t>死亡时，攻击力最高的敌人立即死亡</t>
+  </si>
+  <si>
+    <t>攻击时，被攻击的目标立即死亡（即使自身被打败）</t>
+  </si>
+  <si>
+    <t>死亡时，己方法师立即恢复2点生命值</t>
+  </si>
+  <si>
+    <t>打出时，己方法师的生命值可以变为与 对方法师的生命值相等</t>
+  </si>
+  <si>
+    <t>攻击时，攻击两次</t>
+  </si>
+  <si>
+    <t>若击败了敌方单位，则继续攻击</t>
+  </si>
+  <si>
+    <t>攻击时，可以无视阻挡直接命中对方法师</t>
+  </si>
+  <si>
+    <t>被击败时，手牌中获得一个幽灵（即使已经死亡）</t>
+  </si>
+  <si>
+    <t>每有一个己方的非幽灵动物死亡，手牌中获得一个幽灵（包括自身死亡时）</t>
+  </si>
+  <si>
+    <t>打出时，手牌中获得一个幽灵</t>
+  </si>
+  <si>
+    <t>攻击时，手牌中获得一个幽灵</t>
+  </si>
+  <si>
+    <t>打出时，可以再打出一张手牌</t>
+  </si>
+  <si>
+    <t>每当你有一个动物自爆，可以再打出一张手牌，一回合限一次（包括自身自爆）</t>
+  </si>
+  <si>
+    <t>打出之后的下一回合开始，选择打出手牌行动时可以打出两张</t>
+  </si>
+  <si>
+    <t>被击败时不会死亡，再进行你的回合两次之后死亡（期间再被击败立即死亡）</t>
+  </si>
+  <si>
+    <t>被击败时，你不会死亡而是获得创伤标记，再次受伤则死亡</t>
+  </si>
+  <si>
+    <t>你的防御力锁定为零，但是拥有三点生命值（扣血规则同法师）</t>
+  </si>
+  <si>
+    <t>死亡时进入无敌状态，直到再进行你的回合一次之后才会退场</t>
+  </si>
+  <si>
+    <t>被击败时，你可以使两侧的一个己方动物立即死亡，然后你免疫此击败</t>
+  </si>
+  <si>
     <t>死亡时，可以复活并返回你手牌中（失去强化），但无法立即打出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，可以无视距离限制，攻击对方的任意一个动物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使面前的动物的攻击力减2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的回合时，你可以直接将一张手牌变成灵魂，每回合限一次</t>
+  </si>
+  <si>
+    <t>打出时，获得一个随机灵魂（从剩余卡牌中抽取）</t>
+  </si>
+  <si>
+    <t>两侧动物的攻击力加1</t>
   </si>
   <si>
     <t>两侧动物的防御力加1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>两侧动物的攻击力加1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，对方的实际防御力等于其攻击力或防御力中的较小值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被击败时，你不会死亡而是获得创伤标记，再次受伤则死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使你左边和右边的敌人的防御力均不会超过二</t>
+  </si>
+  <si>
+    <t>使面前的动物的攻击力减2，并且位置无法移动</t>
+  </si>
+  <si>
+    <t>场上每有一个敌方动物，攻击力加一</t>
+  </si>
+  <si>
+    <t>使面前的动物防御力减2</t>
+  </si>
+  <si>
+    <t>打出时，可以立即进行一次全体攻击（不消耗次数）</t>
+  </si>
+  <si>
+    <t>死亡时，可以再打出一张手牌</t>
   </si>
   <si>
     <t>攻击命中对方法师时，额外造成一点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击时可以选择不抵挡（视为此处没有动物）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，可以无视阻挡直接命中对方法师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，可以再打出一张手牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，可以再打出一张手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，可以再打出一张手牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，手牌中获得一个幽灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，手牌中获得一个幽灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被攻击时，手牌中获得一个幽灵（即使已经死亡）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，原地留下一个幽灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，被攻击的目标立即死亡（但自身仍然会受到反击）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击两次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，你会同时攻击左侧和右侧（侧面如果是墙壁则不产生效果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，你会同时攻击左侧和面前（侧面如果是墙壁则不产生效果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时，你会同时攻击面前和右侧（侧面如果是墙壁则不产生效果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时会立即进行一次攻击，但该攻击不能对对方法师造成伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，对方需要立即弃掉一张手牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击后，会立即进行一次攻击（即使已经死亡）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，攻击力最高的敌人死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，会使面前的敌人立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若击败了敌方动物，则继续攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蝎子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野猪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，你的场上的剩余空位都替换为幽灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你两侧的动物受到攻击时，你可以代替承受攻击，但你不会进行反击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>攻击时，即使打平或者失败，也不会因此被击败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被击败时不会死亡，再进行你的回合两次之后死亡（期间再被击败立即死亡）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，可以使己方场上的另一个动物攻击一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>41</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当你场上的动物死亡时，你可以立即将幽灵打出（此效果不可继承）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幽灵</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，若面前的敌人的攻击力小于你，则其立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，所有防御力为一的敌人立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，己方法师立即恢复2点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，己方法师的生命值可以变为与 对方法师的生命值相等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使你左边和右边的敌人的防御力均不会超过二</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>‌对方攻击力最高的单位的攻击无法击败你（但不免疫附加效果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使面前的动物防御力减2</t>
+  </si>
+  <si>
+    <t>身旁存在己方动物时，被攻击时可以选择不抵挡（由己方法师承担攻击）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你两侧的动物被攻击时，你可以代替承受攻击，但进攻者不会被你击败</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -522,9 +518,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
-      <family val="1"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -550,20 +546,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2588,31 +2581,181 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>108856</xdr:colOff>
+      <xdr:colOff>102230</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>68549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>563117</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>515262</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9D7FB49-1A8D-5AA1-15FB-CB8EA4067048}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="102230" y="21921384"/>
+          <a:ext cx="460887" cy="446713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>65617</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>70858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>530812</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>523131</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FFDD72C-FB45-2D6E-E255-A367E9C472D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="65617" y="22394145"/>
+          <a:ext cx="465195" cy="452273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>86139</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>75175</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>569743</xdr:colOff>
+      <xdr:rowOff>31084</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>523485</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>459718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C716591-9743-621B-6AAC-812DC8B24B0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="86139" y="19790532"/>
+          <a:ext cx="437346" cy="428634"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>46953</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>5053</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9D7FB49-1A8D-5AA1-15FB-CB8EA4067048}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
+      <xdr:rowOff>39697</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>492251</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>475718</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="图片 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1324496C-EFB1-F718-4737-54EBEF042560}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2625,44 +2768,44 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="108856" y="19980481"/>
-          <a:ext cx="460887" cy="450837"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>72243</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>31101</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>537438</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>483374</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="图片 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FFDD72C-FB45-2D6E-E255-A367E9C472D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
+          <a:off x="46953" y="20319407"/>
+          <a:ext cx="445298" cy="436021"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>112871</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>124038</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>556843</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD97FAD5-FCD1-881B-8BC7-66817C73937B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2675,8 +2818,58 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="72243" y="20457366"/>
-          <a:ext cx="465195" cy="452273"/>
+          <a:off x="112871" y="20924010"/>
+          <a:ext cx="443972" cy="432045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>120981</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>97914</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>562303</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>526547</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="图片 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C5FE49F-987A-823E-7FB5-598050BEC37F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="120981" y="21454935"/>
+          <a:ext cx="441322" cy="428633"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2975,143 +3168,145 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:H42"/>
+  <dimension ref="B1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="72.33203125" customWidth="1"/>
-    <col min="5" max="8" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="76" customWidth="1"/>
+    <col min="5" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="50.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
-        <v>82</v>
+      <c r="D1" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="E1" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
-        <v>83</v>
+      <c r="D2" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="E2" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
-        <v>100</v>
+      <c r="D3" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="E3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
-        <v>87</v>
+      <c r="D4" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="E4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
-        <v>126</v>
+      <c r="D5" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="E5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
-        <v>78</v>
+      <c r="D6" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
-        <v>111</v>
+      <c r="D7" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3120,18 +3315,18 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
-        <v>91</v>
+      <c r="D8" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -3140,58 +3335,58 @@
         <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
-        <v>86</v>
+      <c r="D9" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>124</v>
+      <c r="D10" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
-        <v>107</v>
+      <c r="D11" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -3200,107 +3395,110 @@
         <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
+        <v>79</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="F12" s="1">
-        <v>4</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>88</v>
+      <c r="D13" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
-        <v>102</v>
+      <c r="D14" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>121</v>
+      <c r="D15" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="E15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D16" t="s">
-        <v>77</v>
+      <c r="D16" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1">
         <v>2</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3310,17 +3508,17 @@
       <c r="C17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>125</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3330,17 +3528,17 @@
       <c r="C18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D18" t="s">
-        <v>115</v>
+      <c r="D18" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3350,8 +3548,8 @@
       <c r="C19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D19" t="s">
-        <v>93</v>
+      <c r="D19" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -3360,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3371,16 +3569,16 @@
         <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
       </c>
       <c r="F20" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3390,8 +3588,8 @@
       <c r="C21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" t="s">
-        <v>99</v>
+      <c r="D21" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -3400,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3410,17 +3608,17 @@
       <c r="C22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D22" t="s">
-        <v>89</v>
+      <c r="D22" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3430,8 +3628,8 @@
       <c r="C23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D23" t="s">
-        <v>80</v>
+      <c r="D23" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3440,7 +3638,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,10 +3646,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>101</v>
+        <v>80</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="E24" s="1">
         <v>5</v>
@@ -3460,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3470,8 +3668,8 @@
       <c r="C25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D25" t="s">
-        <v>85</v>
+      <c r="D25" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="E25" s="1">
         <v>5</v>
@@ -3480,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,17 +3688,17 @@
       <c r="C26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D26" t="s">
-        <v>112</v>
+      <c r="D26" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="E26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3510,17 +3708,17 @@
       <c r="C27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D27" t="s">
-        <v>113</v>
+      <c r="D27" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="E27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3530,17 +3728,17 @@
       <c r="C28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D28" t="s">
-        <v>114</v>
+      <c r="D28" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="E28" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3550,17 +3748,17 @@
       <c r="C29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D29" t="s">
-        <v>96</v>
+      <c r="D29" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="E29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3570,8 +3768,8 @@
       <c r="C30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D30" t="s">
-        <v>79</v>
+      <c r="D30" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -3580,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3590,17 +3788,17 @@
       <c r="C31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D31" t="s">
-        <v>84</v>
+      <c r="D31" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E31" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3610,17 +3808,17 @@
       <c r="C32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>122</v>
+      <c r="D32" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3630,17 +3828,17 @@
       <c r="C33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D33" t="s">
-        <v>98</v>
+      <c r="D33" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
         <v>3</v>
       </c>
-      <c r="F33" s="1">
-        <v>4</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3650,17 +3848,17 @@
       <c r="C34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D34" t="s">
-        <v>94</v>
+      <c r="D34" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3670,8 +3868,8 @@
       <c r="C35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D35" t="s">
-        <v>97</v>
+      <c r="D35" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E35" s="1">
         <v>4</v>
@@ -3680,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3690,17 +3888,17 @@
       <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D36" t="s">
-        <v>123</v>
+      <c r="D36" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="E36" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3708,19 +3906,19 @@
         <v>73</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>92</v>
+        <v>81</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3731,7 +3929,7 @@
         <v>74</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -3740,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3750,8 +3948,8 @@
       <c r="C39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D39" t="s">
-        <v>81</v>
+      <c r="D39" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3760,7 +3958,7 @@
         <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3770,57 +3968,137 @@
       <c r="C40" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D40" t="s">
-        <v>127</v>
+      <c r="D40" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>104</v>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>120</v>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Summon/PicList.xlsx
+++ b/Assets/Resource/Summon/PicList.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551040B9-F05E-4D72-A063-061FD33C52EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4156CF-1A2F-4A94-9A0E-130CFB0270BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,24 +426,12 @@
     <t>打出之后的下一回合开始，选择打出手牌行动时可以打出两张</t>
   </si>
   <si>
-    <t>被击败时不会死亡，再进行你的回合两次之后死亡（期间再被击败立即死亡）</t>
-  </si>
-  <si>
     <t>被击败时，你不会死亡而是获得创伤标记，再次受伤则死亡</t>
   </si>
   <si>
-    <t>你的防御力锁定为零，但是拥有三点生命值（扣血规则同法师）</t>
-  </si>
-  <si>
-    <t>死亡时进入无敌状态，直到再进行你的回合一次之后才会退场</t>
-  </si>
-  <si>
     <t>被击败时，你可以使两侧的一个己方动物立即死亡，然后你免疫此击败</t>
   </si>
   <si>
-    <t>死亡时，可以复活并返回你手牌中（失去强化），但无法立即打出</t>
-  </si>
-  <si>
     <t>你的回合时，你可以直接将一张手牌变成灵魂，每回合限一次</t>
   </si>
   <si>
@@ -485,6 +473,22 @@
   </si>
   <si>
     <t>当你两侧的动物被攻击时，你可以代替承受攻击，但进攻者不会被你击败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击败时进入无敌状态，直到再进行你的回合一次之后才会死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击败时不会死亡，再进行你的回合两次之后死亡，期间再被击败立即死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打出时，使面前的敌人失去所有附加的灵魂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时，可以选择复活并返回你手牌中（失去强化），但不能连续复活</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3206,7 +3210,7 @@
         <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
@@ -3226,7 +3230,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -3266,7 +3270,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -3326,7 +3330,7 @@
         <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -3346,7 +3350,7 @@
         <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
@@ -3426,7 +3430,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
@@ -3469,7 +3473,7 @@
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
@@ -3489,7 +3493,7 @@
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -3509,7 +3513,7 @@
         <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -3549,7 +3553,7 @@
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -3629,7 +3633,7 @@
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3669,7 +3673,7 @@
         <v>61</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E25" s="1">
         <v>5</v>
@@ -3689,7 +3693,7 @@
         <v>62</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3769,7 +3773,7 @@
         <v>66</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -3789,7 +3793,7 @@
         <v>67</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E31" s="1">
         <v>4</v>
@@ -3809,7 +3813,7 @@
         <v>68</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -3829,7 +3833,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3949,7 +3953,7 @@
         <v>75</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3969,7 +3973,7 @@
         <v>76</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -4009,7 +4013,7 @@
         <v>92</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E42" s="1">
         <v>4</v>
